--- a/EndResult/400m Fri.xlsx
+++ b/EndResult/400m Fri.xlsx
@@ -1308,7 +1308,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Maria Erikovna Alvestad</t>
+          <t>Elise Lund</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17.03.2023</t>
+          <t>19.01.2018</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Elise Lund</t>
+          <t>Maria Erikovna Alvestad</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>19.01.2018</t>
+          <t>17.03.2023</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1413,25 +1413,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Monica Martinsen</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.40,30</t>
+          <t>4.40,00</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23.09.2007</t>
+          <t>29.05.2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1448,25 +1448,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sara Juul Wolfgang</t>
+          <t>Monica Martinsen</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.41,17</t>
+          <t>4.40,30</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16.01.2015</t>
+          <t>23.09.2007</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1483,25 +1483,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Åse Vigdisdatter Nytrø</t>
+          <t>Sara Juul Wolfgang</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.41,86</t>
+          <t>4.41,17</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10.02.2012</t>
+          <t>16.01.2015</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1518,25 +1518,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Christiana Bjørkli</t>
+          <t>Åse Vigdisdatter Nytrø</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.44,36</t>
+          <t>4.41,86</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>23.09.2007</t>
+          <t>10.02.2012</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1553,25 +1553,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Siv Flatås Hoddø</t>
+          <t>Christiana Bjørkli</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.44,70</t>
+          <t>4.44,36</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18.09.2011</t>
+          <t>23.09.2007</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1588,20 +1588,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Irja Gravdahl</t>
+          <t>Siv Flatås Hoddø</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4.47,27</t>
+          <t>4.44,70</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>521</v>
+        <v>536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>21.01.2011</t>
+          <t>18.09.2011</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
